--- a/attendance/2026-05-09.xlsx
+++ b/attendance/2026-05-09.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>04:19:39</t>
+          <t>15:35:57</t>
         </is>
       </c>
     </row>
